--- a/migration_mimu_data/town.xlsx
+++ b/migration_mimu_data/town.xlsx
@@ -7380,7 +7380,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7398,12 +7398,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -7512,7 +7506,7 @@
     <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="15" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -7527,13 +7521,13 @@
     <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -7875,7 +7869,7 @@
     <col min="23" max="23" style="3" width="11.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5" hidden="1">
       <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
@@ -7946,7 +7940,7 @@
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5" hidden="1">
       <c r="A2" s="2" t="s">
         <v>114</v>
       </c>
@@ -8005,7 +7999,7 @@
       <c r="V2" s="9"/>
       <c r="W2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="16.5" hidden="1">
       <c r="A3" s="2" t="s">
         <v>114</v>
       </c>
@@ -8064,7 +8058,7 @@
       <c r="V3" s="9"/>
       <c r="W3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="16.5" hidden="1">
       <c r="A4" s="2" t="s">
         <v>114</v>
       </c>
@@ -8123,7 +8117,7 @@
       <c r="V4" s="9"/>
       <c r="W4" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="16.5" hidden="1">
       <c r="A5" s="2" t="s">
         <v>114</v>
       </c>
@@ -8182,7 +8176,7 @@
       <c r="V5" s="9"/>
       <c r="W5" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="16.5" hidden="1">
       <c r="A6" s="2" t="s">
         <v>114</v>
       </c>
@@ -8245,7 +8239,7 @@
       <c r="V6" s="9"/>
       <c r="W6" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="16.5" hidden="1">
       <c r="A7" s="2" t="s">
         <v>114</v>
       </c>
@@ -8304,7 +8298,7 @@
       <c r="V7" s="9"/>
       <c r="W7" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="16.5" hidden="1">
       <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
@@ -8367,7 +8361,7 @@
       <c r="V8" s="9"/>
       <c r="W8" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="16.5" hidden="1">
       <c r="A9" s="2" t="s">
         <v>114</v>
       </c>
@@ -8430,7 +8424,7 @@
       <c r="V9" s="9"/>
       <c r="W9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="16.5" hidden="1">
       <c r="A10" s="2" t="s">
         <v>114</v>
       </c>
@@ -8489,7 +8483,7 @@
       <c r="V10" s="9"/>
       <c r="W10" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="16.5" hidden="1">
       <c r="A11" s="2" t="s">
         <v>114</v>
       </c>
@@ -8552,7 +8546,7 @@
       <c r="V11" s="9"/>
       <c r="W11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="16.5" hidden="1">
       <c r="A12" s="2" t="s">
         <v>114</v>
       </c>
@@ -8611,7 +8605,7 @@
       <c r="V12" s="9"/>
       <c r="W12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="16.5" hidden="1">
       <c r="A13" s="2" t="s">
         <v>114</v>
       </c>
@@ -8670,7 +8664,7 @@
       <c r="V13" s="9"/>
       <c r="W13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="16.5" hidden="1">
       <c r="A14" s="2" t="s">
         <v>114</v>
       </c>
@@ -8733,7 +8727,7 @@
       <c r="V14" s="9"/>
       <c r="W14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="16.5" hidden="1">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
@@ -8792,7 +8786,7 @@
       <c r="V15" s="9"/>
       <c r="W15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="16.5" hidden="1">
       <c r="A16" s="2" t="s">
         <v>114</v>
       </c>
@@ -8851,7 +8845,7 @@
       <c r="V16" s="9"/>
       <c r="W16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="16.5" hidden="1">
       <c r="A17" s="2" t="s">
         <v>114</v>
       </c>
@@ -8914,7 +8908,7 @@
       <c r="V17" s="9"/>
       <c r="W17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="16.5" hidden="1">
       <c r="A18" s="2" t="s">
         <v>114</v>
       </c>
@@ -8973,7 +8967,7 @@
       <c r="V18" s="9"/>
       <c r="W18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="16.5" hidden="1">
       <c r="A19" s="2" t="s">
         <v>114</v>
       </c>
@@ -9040,7 +9034,7 @@
         <v>204</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="25.5">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="16.5" hidden="1">
       <c r="A20" s="2" t="s">
         <v>114</v>
       </c>
@@ -9103,7 +9097,7 @@
       <c r="V20" s="9"/>
       <c r="W20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="16.5" hidden="1">
       <c r="A21" s="2" t="s">
         <v>114</v>
       </c>
@@ -9162,7 +9156,7 @@
       <c r="V21" s="9"/>
       <c r="W21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="16.5" hidden="1">
       <c r="A22" s="2" t="s">
         <v>114</v>
       </c>
@@ -9221,7 +9215,7 @@
       <c r="V22" s="9"/>
       <c r="W22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="16.5" hidden="1">
       <c r="A23" s="2" t="s">
         <v>114</v>
       </c>
@@ -9280,7 +9274,7 @@
       <c r="V23" s="9"/>
       <c r="W23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="16.5" hidden="1">
       <c r="A24" s="2" t="s">
         <v>114</v>
       </c>
@@ -9339,7 +9333,7 @@
       <c r="V24" s="9"/>
       <c r="W24" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="16.5" hidden="1">
       <c r="A25" s="2" t="s">
         <v>114</v>
       </c>
@@ -9398,7 +9392,7 @@
       <c r="V25" s="9"/>
       <c r="W25" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="16.5" hidden="1">
       <c r="A26" s="2" t="s">
         <v>114</v>
       </c>
@@ -9461,7 +9455,7 @@
       <c r="V26" s="9"/>
       <c r="W26" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="16.5" hidden="1">
       <c r="A27" s="2" t="s">
         <v>114</v>
       </c>
@@ -9520,7 +9514,7 @@
       <c r="V27" s="9"/>
       <c r="W27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="16.5" hidden="1">
       <c r="A28" s="2" t="s">
         <v>114</v>
       </c>
@@ -9579,7 +9573,7 @@
       <c r="V28" s="9"/>
       <c r="W28" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="16.5" hidden="1">
       <c r="A29" s="2" t="s">
         <v>114</v>
       </c>
@@ -9638,7 +9632,7 @@
       <c r="V29" s="9"/>
       <c r="W29" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="16.5" hidden="1">
       <c r="A30" s="2" t="s">
         <v>114</v>
       </c>
@@ -9697,7 +9691,7 @@
       <c r="V30" s="9"/>
       <c r="W30" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="16.5" hidden="1">
       <c r="A31" s="2" t="s">
         <v>114</v>
       </c>
@@ -9756,7 +9750,7 @@
       <c r="V31" s="9"/>
       <c r="W31" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="16.5" hidden="1">
       <c r="A32" s="2" t="s">
         <v>114</v>
       </c>
@@ -9815,7 +9809,7 @@
       <c r="V32" s="9"/>
       <c r="W32" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="16.5" hidden="1">
       <c r="A33" s="2" t="s">
         <v>114</v>
       </c>
@@ -9874,7 +9868,7 @@
       <c r="V33" s="9"/>
       <c r="W33" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="16.5" hidden="1">
       <c r="A34" s="2" t="s">
         <v>114</v>
       </c>
@@ -9933,7 +9927,7 @@
       <c r="V34" s="9"/>
       <c r="W34" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="16.5" hidden="1">
       <c r="A35" s="2" t="s">
         <v>114</v>
       </c>
@@ -9996,7 +9990,7 @@
       <c r="V35" s="9"/>
       <c r="W35" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="16.5" hidden="1">
       <c r="A36" s="2" t="s">
         <v>114</v>
       </c>
@@ -10055,7 +10049,7 @@
       <c r="V36" s="9"/>
       <c r="W36" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="16.5" hidden="1">
       <c r="A37" s="2" t="s">
         <v>114</v>
       </c>
@@ -10114,7 +10108,7 @@
       <c r="V37" s="9"/>
       <c r="W37" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="16.5" hidden="1">
       <c r="A38" s="2" t="s">
         <v>114</v>
       </c>
@@ -10173,7 +10167,7 @@
       <c r="V38" s="9"/>
       <c r="W38" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="16.5" hidden="1">
       <c r="A39" s="2" t="s">
         <v>114</v>
       </c>
@@ -10232,7 +10226,7 @@
       <c r="V39" s="9"/>
       <c r="W39" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="16.5" hidden="1">
       <c r="A40" s="2" t="s">
         <v>114</v>
       </c>
@@ -10291,7 +10285,7 @@
       <c r="V40" s="9"/>
       <c r="W40" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="16.5" hidden="1">
       <c r="A41" s="2" t="s">
         <v>114</v>
       </c>
@@ -10350,7 +10344,7 @@
       <c r="V41" s="9"/>
       <c r="W41" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="16.5" hidden="1">
       <c r="A42" s="2" t="s">
         <v>114</v>
       </c>
@@ -10413,7 +10407,7 @@
       <c r="V42" s="9"/>
       <c r="W42" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="16.5" hidden="1">
       <c r="A43" s="2" t="s">
         <v>114</v>
       </c>
@@ -10472,7 +10466,7 @@
       <c r="V43" s="9"/>
       <c r="W43" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="16.5" hidden="1">
       <c r="A44" s="2" t="s">
         <v>114</v>
       </c>
@@ -10535,7 +10529,7 @@
       <c r="V44" s="9"/>
       <c r="W44" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="16.5" hidden="1">
       <c r="A45" s="2" t="s">
         <v>114</v>
       </c>
@@ -10594,7 +10588,7 @@
       <c r="V45" s="9"/>
       <c r="W45" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="16.5" hidden="1">
       <c r="A46" s="2" t="s">
         <v>114</v>
       </c>
@@ -10653,7 +10647,7 @@
       <c r="V46" s="9"/>
       <c r="W46" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="16.5" hidden="1">
       <c r="A47" s="2" t="s">
         <v>114</v>
       </c>
@@ -10712,7 +10706,7 @@
       <c r="V47" s="9"/>
       <c r="W47" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="16.5" hidden="1">
       <c r="A48" s="2" t="s">
         <v>300</v>
       </c>
@@ -10771,7 +10765,7 @@
       <c r="V48" s="9"/>
       <c r="W48" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="16.5" hidden="1">
       <c r="A49" s="2" t="s">
         <v>300</v>
       </c>
@@ -10834,7 +10828,7 @@
       <c r="V49" s="9"/>
       <c r="W49" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="16.5" hidden="1">
       <c r="A50" s="2" t="s">
         <v>300</v>
       </c>
@@ -10897,7 +10891,7 @@
       <c r="V50" s="9"/>
       <c r="W50" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="16.5" hidden="1">
       <c r="A51" s="2" t="s">
         <v>300</v>
       </c>
@@ -10956,7 +10950,7 @@
       <c r="V51" s="9"/>
       <c r="W51" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="16.5" hidden="1">
       <c r="A52" s="2" t="s">
         <v>300</v>
       </c>
@@ -11015,7 +11009,7 @@
       <c r="V52" s="9"/>
       <c r="W52" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="16.5" hidden="1">
       <c r="A53" s="2" t="s">
         <v>300</v>
       </c>
@@ -11074,7 +11068,7 @@
       <c r="V53" s="9"/>
       <c r="W53" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="16.5" hidden="1">
       <c r="A54" s="2" t="s">
         <v>300</v>
       </c>
@@ -11137,7 +11131,7 @@
       <c r="V54" s="9"/>
       <c r="W54" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="16.5" hidden="1">
       <c r="A55" s="2" t="s">
         <v>300</v>
       </c>
@@ -11196,7 +11190,7 @@
       <c r="V55" s="9"/>
       <c r="W55" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="16.5" hidden="1">
       <c r="A56" s="2" t="s">
         <v>300</v>
       </c>
@@ -11259,7 +11253,7 @@
       <c r="V56" s="9"/>
       <c r="W56" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="16.5" hidden="1">
       <c r="A57" s="2" t="s">
         <v>300</v>
       </c>
@@ -11318,7 +11312,7 @@
       <c r="V57" s="9"/>
       <c r="W57" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="16.5" hidden="1">
       <c r="A58" s="2" t="s">
         <v>300</v>
       </c>
@@ -11377,7 +11371,7 @@
       <c r="V58" s="9"/>
       <c r="W58" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="16.5" hidden="1">
       <c r="A59" s="2" t="s">
         <v>300</v>
       </c>
@@ -11436,7 +11430,7 @@
       <c r="V59" s="9"/>
       <c r="W59" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="16.5" hidden="1">
       <c r="A60" s="2" t="s">
         <v>300</v>
       </c>
@@ -11495,7 +11489,7 @@
       <c r="V60" s="9"/>
       <c r="W60" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="16.5" hidden="1">
       <c r="A61" s="2" t="s">
         <v>300</v>
       </c>
@@ -11558,7 +11552,7 @@
       <c r="V61" s="9"/>
       <c r="W61" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="16.5" hidden="1">
       <c r="A62" s="2" t="s">
         <v>300</v>
       </c>
@@ -11617,7 +11611,7 @@
       <c r="V62" s="9"/>
       <c r="W62" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="16.5" hidden="1">
       <c r="A63" s="2" t="s">
         <v>300</v>
       </c>
@@ -11680,7 +11674,7 @@
       <c r="V63" s="9"/>
       <c r="W63" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="16.5" hidden="1">
       <c r="A64" s="2" t="s">
         <v>300</v>
       </c>
@@ -11739,7 +11733,7 @@
       <c r="V64" s="9"/>
       <c r="W64" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="16.5" hidden="1">
       <c r="A65" s="2" t="s">
         <v>300</v>
       </c>
@@ -11802,7 +11796,7 @@
       <c r="V65" s="9"/>
       <c r="W65" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="16.5" hidden="1">
       <c r="A66" s="2" t="s">
         <v>300</v>
       </c>
@@ -11861,7 +11855,7 @@
       <c r="V66" s="9"/>
       <c r="W66" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="16.5" hidden="1">
       <c r="A67" s="2" t="s">
         <v>300</v>
       </c>
@@ -11924,7 +11918,7 @@
       <c r="V67" s="9"/>
       <c r="W67" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="16.5" hidden="1">
       <c r="A68" s="2" t="s">
         <v>300</v>
       </c>
@@ -11983,7 +11977,7 @@
       <c r="V68" s="9"/>
       <c r="W68" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="16.5" hidden="1">
       <c r="A69" s="2" t="s">
         <v>300</v>
       </c>
@@ -12042,7 +12036,7 @@
       <c r="V69" s="9"/>
       <c r="W69" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="16.5" hidden="1">
       <c r="A70" s="2" t="s">
         <v>300</v>
       </c>
@@ -12101,7 +12095,7 @@
       <c r="V70" s="9"/>
       <c r="W70" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="16.5" hidden="1">
       <c r="A71" s="2" t="s">
         <v>300</v>
       </c>
@@ -12160,7 +12154,7 @@
       <c r="V71" s="9"/>
       <c r="W71" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="16.5" hidden="1">
       <c r="A72" s="2" t="s">
         <v>300</v>
       </c>
@@ -12219,7 +12213,7 @@
       <c r="V72" s="9"/>
       <c r="W72" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="16.5" hidden="1">
       <c r="A73" s="2" t="s">
         <v>300</v>
       </c>
@@ -12282,7 +12276,7 @@
       <c r="V73" s="9"/>
       <c r="W73" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="16.5" hidden="1">
       <c r="A74" s="2" t="s">
         <v>300</v>
       </c>
@@ -12345,7 +12339,7 @@
       <c r="V74" s="9"/>
       <c r="W74" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="16.5" hidden="1">
       <c r="A75" s="2" t="s">
         <v>300</v>
       </c>
@@ -12408,7 +12402,7 @@
       <c r="V75" s="9"/>
       <c r="W75" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="16.5" hidden="1">
       <c r="A76" s="2" t="s">
         <v>300</v>
       </c>
@@ -12467,7 +12461,7 @@
       <c r="V76" s="9"/>
       <c r="W76" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="16.5" hidden="1">
       <c r="A77" s="2" t="s">
         <v>414</v>
       </c>
@@ -12526,7 +12520,7 @@
       <c r="V77" s="9"/>
       <c r="W77" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="16.5" hidden="1">
       <c r="A78" s="2" t="s">
         <v>414</v>
       </c>
@@ -12585,7 +12579,7 @@
       <c r="V78" s="9"/>
       <c r="W78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="16.5" hidden="1">
       <c r="A79" s="2" t="s">
         <v>414</v>
       </c>
@@ -12644,7 +12638,7 @@
       <c r="V79" s="9"/>
       <c r="W79" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="16.5" hidden="1">
       <c r="A80" s="2" t="s">
         <v>414</v>
       </c>
@@ -12707,7 +12701,7 @@
       <c r="V80" s="9"/>
       <c r="W80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="16.5" hidden="1">
       <c r="A81" s="2" t="s">
         <v>414</v>
       </c>
@@ -12766,7 +12760,7 @@
       <c r="V81" s="9"/>
       <c r="W81" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="16.5" hidden="1">
       <c r="A82" s="2" t="s">
         <v>414</v>
       </c>
@@ -12825,7 +12819,7 @@
       <c r="V82" s="9"/>
       <c r="W82" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="16.5" hidden="1">
       <c r="A83" s="2" t="s">
         <v>414</v>
       </c>
@@ -12888,7 +12882,7 @@
       <c r="V83" s="9"/>
       <c r="W83" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="16.5" hidden="1">
       <c r="A84" s="2" t="s">
         <v>414</v>
       </c>
@@ -12951,7 +12945,7 @@
       <c r="V84" s="9"/>
       <c r="W84" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="16.5" hidden="1">
       <c r="A85" s="2" t="s">
         <v>414</v>
       </c>
@@ -13010,7 +13004,7 @@
       <c r="V85" s="9"/>
       <c r="W85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="16.5" hidden="1">
       <c r="A86" s="2" t="s">
         <v>414</v>
       </c>
@@ -13073,7 +13067,7 @@
       <c r="V86" s="9"/>
       <c r="W86" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="16.5" hidden="1">
       <c r="A87" s="2" t="s">
         <v>414</v>
       </c>
@@ -13132,7 +13126,7 @@
       <c r="V87" s="9"/>
       <c r="W87" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="16.5" hidden="1">
       <c r="A88" s="2" t="s">
         <v>414</v>
       </c>
@@ -13191,7 +13185,7 @@
       <c r="V88" s="9"/>
       <c r="W88" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="16.5" hidden="1">
       <c r="A89" s="2" t="s">
         <v>414</v>
       </c>
@@ -13250,7 +13244,7 @@
       <c r="V89" s="9"/>
       <c r="W89" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="16.5" hidden="1">
       <c r="A90" s="2" t="s">
         <v>414</v>
       </c>
@@ -13313,7 +13307,7 @@
       <c r="V90" s="9"/>
       <c r="W90" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="16.5" hidden="1">
       <c r="A91" s="2" t="s">
         <v>414</v>
       </c>
@@ -13372,7 +13366,7 @@
       <c r="V91" s="9"/>
       <c r="W91" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="16.5" hidden="1">
       <c r="A92" s="2" t="s">
         <v>414</v>
       </c>
@@ -13431,7 +13425,7 @@
       <c r="V92" s="9"/>
       <c r="W92" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="16.5" hidden="1">
       <c r="A93" s="2" t="s">
         <v>414</v>
       </c>
@@ -13490,7 +13484,7 @@
       <c r="V93" s="9"/>
       <c r="W93" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="16.5" hidden="1">
       <c r="A94" s="2" t="s">
         <v>414</v>
       </c>
@@ -13549,7 +13543,7 @@
       <c r="V94" s="9"/>
       <c r="W94" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="16.5" hidden="1">
       <c r="A95" s="2" t="s">
         <v>414</v>
       </c>
@@ -13612,7 +13606,7 @@
       <c r="V95" s="9"/>
       <c r="W95" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="16.5" hidden="1">
       <c r="A96" s="2" t="s">
         <v>414</v>
       </c>
@@ -13675,7 +13669,7 @@
       <c r="V96" s="9"/>
       <c r="W96" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="16.5" hidden="1">
       <c r="A97" s="2" t="s">
         <v>414</v>
       </c>
@@ -13738,7 +13732,7 @@
       <c r="V97" s="9"/>
       <c r="W97" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="16.5" hidden="1">
       <c r="A98" s="2" t="s">
         <v>414</v>
       </c>
@@ -13797,7 +13791,7 @@
       <c r="V98" s="9"/>
       <c r="W98" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="16.5" hidden="1">
       <c r="A99" s="2" t="s">
         <v>414</v>
       </c>
@@ -13856,7 +13850,7 @@
       <c r="V99" s="9"/>
       <c r="W99" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="16.5" hidden="1">
       <c r="A100" s="2" t="s">
         <v>506</v>
       </c>
@@ -13915,7 +13909,7 @@
       <c r="V100" s="9"/>
       <c r="W100" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="16.5" hidden="1">
       <c r="A101" s="2" t="s">
         <v>506</v>
       </c>
@@ -13974,7 +13968,7 @@
       <c r="V101" s="9"/>
       <c r="W101" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="16.5" hidden="1">
       <c r="A102" s="2" t="s">
         <v>506</v>
       </c>
@@ -14037,7 +14031,7 @@
       <c r="V102" s="9"/>
       <c r="W102" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="16.5" hidden="1">
       <c r="A103" s="2" t="s">
         <v>506</v>
       </c>
@@ -14096,7 +14090,7 @@
       <c r="V103" s="9"/>
       <c r="W103" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="16.5" hidden="1">
       <c r="A104" s="2" t="s">
         <v>506</v>
       </c>
@@ -14159,7 +14153,7 @@
       <c r="V104" s="9"/>
       <c r="W104" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="16.5" hidden="1">
       <c r="A105" s="2" t="s">
         <v>506</v>
       </c>
@@ -14218,7 +14212,7 @@
       <c r="V105" s="9"/>
       <c r="W105" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="16.5" hidden="1">
       <c r="A106" s="2" t="s">
         <v>506</v>
       </c>
@@ -14281,7 +14275,7 @@
       <c r="V106" s="9"/>
       <c r="W106" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="16.5" hidden="1">
       <c r="A107" s="2" t="s">
         <v>506</v>
       </c>
@@ -14344,7 +14338,7 @@
       <c r="V107" s="9"/>
       <c r="W107" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="16.5" hidden="1">
       <c r="A108" s="2" t="s">
         <v>506</v>
       </c>
@@ -14403,7 +14397,7 @@
       <c r="V108" s="9"/>
       <c r="W108" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="16.5" hidden="1">
       <c r="A109" s="2" t="s">
         <v>506</v>
       </c>
@@ -14584,7 +14578,7 @@
       <c r="V111" s="9"/>
       <c r="W111" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="16.5" hidden="1">
       <c r="A112" s="2" t="s">
         <v>506</v>
       </c>
@@ -14643,7 +14637,7 @@
       <c r="V112" s="9"/>
       <c r="W112" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="16.5" hidden="1">
       <c r="A113" s="2" t="s">
         <v>506</v>
       </c>
@@ -14706,7 +14700,7 @@
       <c r="V113" s="9"/>
       <c r="W113" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="16.5" hidden="1">
       <c r="A114" s="2" t="s">
         <v>506</v>
       </c>
@@ -14769,7 +14763,7 @@
       <c r="V114" s="9"/>
       <c r="W114" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="16.5" hidden="1">
       <c r="A115" s="2" t="s">
         <v>506</v>
       </c>
@@ -14828,7 +14822,7 @@
       <c r="V115" s="9"/>
       <c r="W115" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="16.5" hidden="1">
       <c r="A116" s="2" t="s">
         <v>506</v>
       </c>
@@ -14891,7 +14885,7 @@
       <c r="V116" s="9"/>
       <c r="W116" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="16.5" hidden="1">
       <c r="A117" s="2" t="s">
         <v>506</v>
       </c>
@@ -14950,7 +14944,7 @@
       <c r="V117" s="9"/>
       <c r="W117" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="16.5" hidden="1">
       <c r="A118" s="2" t="s">
         <v>506</v>
       </c>
@@ -15009,7 +15003,7 @@
       <c r="V118" s="9"/>
       <c r="W118" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="16.5" hidden="1">
       <c r="A119" s="2" t="s">
         <v>506</v>
       </c>
@@ -15068,7 +15062,7 @@
       <c r="V119" s="9"/>
       <c r="W119" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="16.5" hidden="1">
       <c r="A120" s="2" t="s">
         <v>587</v>
       </c>
@@ -15127,7 +15121,7 @@
       <c r="V120" s="9"/>
       <c r="W120" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="16.5" hidden="1">
       <c r="A121" s="2" t="s">
         <v>587</v>
       </c>
@@ -15186,7 +15180,7 @@
       <c r="V121" s="9"/>
       <c r="W121" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="16.5" hidden="1">
       <c r="A122" s="2" t="s">
         <v>587</v>
       </c>
@@ -15249,7 +15243,7 @@
       <c r="V122" s="9"/>
       <c r="W122" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="16.5" hidden="1">
       <c r="A123" s="2" t="s">
         <v>587</v>
       </c>
@@ -15308,7 +15302,7 @@
       <c r="V123" s="9"/>
       <c r="W123" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="16.5" hidden="1">
       <c r="A124" s="2" t="s">
         <v>587</v>
       </c>
@@ -15367,7 +15361,7 @@
       <c r="V124" s="9"/>
       <c r="W124" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="16.5" hidden="1">
       <c r="A125" s="2" t="s">
         <v>587</v>
       </c>
@@ -15426,7 +15420,7 @@
       <c r="V125" s="9"/>
       <c r="W125" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="16.5" hidden="1">
       <c r="A126" s="2" t="s">
         <v>587</v>
       </c>
@@ -15485,7 +15479,7 @@
       <c r="V126" s="9"/>
       <c r="W126" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="16.5" hidden="1">
       <c r="A127" s="2" t="s">
         <v>587</v>
       </c>
@@ -15544,7 +15538,7 @@
       <c r="V127" s="9"/>
       <c r="W127" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="16.5" hidden="1">
       <c r="A128" s="2" t="s">
         <v>587</v>
       </c>
@@ -15603,7 +15597,7 @@
       <c r="V128" s="9"/>
       <c r="W128" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="16.5" hidden="1">
       <c r="A129" s="2" t="s">
         <v>587</v>
       </c>
@@ -15662,7 +15656,7 @@
       <c r="V129" s="9"/>
       <c r="W129" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="16.5" hidden="1">
       <c r="A130" s="2" t="s">
         <v>587</v>
       </c>
@@ -15725,7 +15719,7 @@
       <c r="V130" s="9"/>
       <c r="W130" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="16.5" hidden="1">
       <c r="A131" s="2" t="s">
         <v>587</v>
       </c>
@@ -15784,7 +15778,7 @@
       <c r="V131" s="9"/>
       <c r="W131" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="16.5" hidden="1">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -15847,7 +15841,7 @@
       <c r="V132" s="9"/>
       <c r="W132" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="16.5" hidden="1">
       <c r="A133" s="2" t="s">
         <v>587</v>
       </c>
@@ -15906,7 +15900,7 @@
       <c r="V133" s="9"/>
       <c r="W133" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="16.5" hidden="1">
       <c r="A134" s="2" t="s">
         <v>587</v>
       </c>
@@ -15969,7 +15963,7 @@
       <c r="V134" s="9"/>
       <c r="W134" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="16.5" hidden="1">
       <c r="A135" s="2" t="s">
         <v>587</v>
       </c>
@@ -16032,7 +16026,7 @@
       <c r="V135" s="9"/>
       <c r="W135" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="16.5" hidden="1">
       <c r="A136" s="2" t="s">
         <v>587</v>
       </c>
@@ -16091,7 +16085,7 @@
       <c r="V136" s="9"/>
       <c r="W136" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="16.5" hidden="1">
       <c r="A137" s="2" t="s">
         <v>587</v>
       </c>
@@ -16150,7 +16144,7 @@
       <c r="V137" s="9"/>
       <c r="W137" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="16.5" hidden="1">
       <c r="A138" s="2" t="s">
         <v>587</v>
       </c>
@@ -16209,7 +16203,7 @@
       <c r="V138" s="9"/>
       <c r="W138" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="16.5" hidden="1">
       <c r="A139" s="2" t="s">
         <v>587</v>
       </c>
@@ -16268,7 +16262,7 @@
       <c r="V139" s="9"/>
       <c r="W139" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="16.5" hidden="1">
       <c r="A140" s="2" t="s">
         <v>587</v>
       </c>
@@ -16327,7 +16321,7 @@
       <c r="V140" s="9"/>
       <c r="W140" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="16.5" hidden="1">
       <c r="A141" s="2" t="s">
         <v>587</v>
       </c>
@@ -16386,7 +16380,7 @@
       <c r="V141" s="9"/>
       <c r="W141" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="16.5" hidden="1">
       <c r="A142" s="2" t="s">
         <v>587</v>
       </c>
@@ -16445,7 +16439,7 @@
       <c r="V142" s="9"/>
       <c r="W142" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="16.5" hidden="1">
       <c r="A143" s="2" t="s">
         <v>587</v>
       </c>
@@ -16504,7 +16498,7 @@
       <c r="V143" s="9"/>
       <c r="W143" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="16.5" hidden="1">
       <c r="A144" s="2" t="s">
         <v>587</v>
       </c>
@@ -16563,7 +16557,7 @@
       <c r="V144" s="9"/>
       <c r="W144" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="16.5" hidden="1">
       <c r="A145" s="2" t="s">
         <v>587</v>
       </c>
@@ -16622,7 +16616,7 @@
       <c r="V145" s="9"/>
       <c r="W145" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="16.5" hidden="1">
       <c r="A146" s="2" t="s">
         <v>587</v>
       </c>
@@ -16681,7 +16675,7 @@
       <c r="V146" s="9"/>
       <c r="W146" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="16.5" hidden="1">
       <c r="A147" s="2" t="s">
         <v>587</v>
       </c>
@@ -16740,7 +16734,7 @@
       <c r="V147" s="9"/>
       <c r="W147" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="16.5" hidden="1">
       <c r="A148" s="2" t="s">
         <v>587</v>
       </c>
@@ -16799,7 +16793,7 @@
       <c r="V148" s="9"/>
       <c r="W148" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="16.5" hidden="1">
       <c r="A149" s="2" t="s">
         <v>587</v>
       </c>
@@ -16858,7 +16852,7 @@
       <c r="V149" s="9"/>
       <c r="W149" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="16.5" hidden="1">
       <c r="A150" s="2" t="s">
         <v>587</v>
       </c>
@@ -16921,7 +16915,7 @@
       <c r="V150" s="9"/>
       <c r="W150" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="16.5" hidden="1">
       <c r="A151" s="2" t="s">
         <v>587</v>
       </c>
@@ -16980,7 +16974,7 @@
       <c r="V151" s="9"/>
       <c r="W151" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="16.5" hidden="1">
       <c r="A152" s="2" t="s">
         <v>587</v>
       </c>
@@ -17039,7 +17033,7 @@
       <c r="V152" s="9"/>
       <c r="W152" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="16.5" hidden="1">
       <c r="A153" s="2" t="s">
         <v>714</v>
       </c>
@@ -17098,7 +17092,7 @@
       <c r="V153" s="9"/>
       <c r="W153" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="16.5" hidden="1">
       <c r="A154" s="2" t="s">
         <v>714</v>
       </c>
@@ -17157,7 +17151,7 @@
       <c r="V154" s="9"/>
       <c r="W154" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="16.5" hidden="1">
       <c r="A155" s="2" t="s">
         <v>714</v>
       </c>
@@ -17216,7 +17210,7 @@
       <c r="V155" s="9"/>
       <c r="W155" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="16.5" hidden="1">
       <c r="A156" s="2" t="s">
         <v>714</v>
       </c>
@@ -17279,7 +17273,7 @@
       <c r="V156" s="9"/>
       <c r="W156" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="16.5" hidden="1">
       <c r="A157" s="2" t="s">
         <v>714</v>
       </c>
@@ -17338,7 +17332,7 @@
       <c r="V157" s="9"/>
       <c r="W157" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="16.5" hidden="1">
       <c r="A158" s="2" t="s">
         <v>714</v>
       </c>
@@ -17397,7 +17391,7 @@
       <c r="V158" s="9"/>
       <c r="W158" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="16.5" hidden="1">
       <c r="A159" s="2" t="s">
         <v>714</v>
       </c>
@@ -17460,7 +17454,7 @@
       <c r="V159" s="9"/>
       <c r="W159" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="16.5" hidden="1">
       <c r="A160" s="2" t="s">
         <v>714</v>
       </c>
@@ -17519,7 +17513,7 @@
       <c r="V160" s="9"/>
       <c r="W160" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="16.5" hidden="1">
       <c r="A161" s="2" t="s">
         <v>714</v>
       </c>
@@ -17582,7 +17576,7 @@
       <c r="V161" s="9"/>
       <c r="W161" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="16.5" hidden="1">
       <c r="A162" s="2" t="s">
         <v>714</v>
       </c>
@@ -17641,7 +17635,7 @@
       <c r="V162" s="9"/>
       <c r="W162" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="16.5" hidden="1">
       <c r="A163" s="2" t="s">
         <v>714</v>
       </c>
@@ -17700,7 +17694,7 @@
       <c r="V163" s="9"/>
       <c r="W163" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="16.5" hidden="1">
       <c r="A164" s="2" t="s">
         <v>760</v>
       </c>
@@ -17759,7 +17753,7 @@
       <c r="V164" s="9"/>
       <c r="W164" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="16.5" hidden="1">
       <c r="A165" s="2" t="s">
         <v>760</v>
       </c>
@@ -17818,7 +17812,7 @@
       <c r="V165" s="9"/>
       <c r="W165" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="16.5" hidden="1">
       <c r="A166" s="2" t="s">
         <v>760</v>
       </c>
@@ -17881,7 +17875,7 @@
       <c r="V166" s="9"/>
       <c r="W166" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="16.5" hidden="1">
       <c r="A167" s="2" t="s">
         <v>760</v>
       </c>
@@ -17940,7 +17934,7 @@
       <c r="V167" s="9"/>
       <c r="W167" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="16.5" hidden="1">
       <c r="A168" s="2" t="s">
         <v>760</v>
       </c>
@@ -17999,7 +17993,7 @@
       <c r="V168" s="9"/>
       <c r="W168" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="16.5" hidden="1">
       <c r="A169" s="2" t="s">
         <v>760</v>
       </c>
@@ -18058,7 +18052,7 @@
       <c r="V169" s="9"/>
       <c r="W169" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="16.5" hidden="1">
       <c r="A170" s="2" t="s">
         <v>760</v>
       </c>
@@ -18117,7 +18111,7 @@
       <c r="V170" s="9"/>
       <c r="W170" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="16.5" hidden="1">
       <c r="A171" s="2" t="s">
         <v>760</v>
       </c>
@@ -18176,7 +18170,7 @@
       <c r="V171" s="9"/>
       <c r="W171" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="16.5" hidden="1">
       <c r="A172" s="2" t="s">
         <v>760</v>
       </c>
@@ -18235,7 +18229,7 @@
       <c r="V172" s="9"/>
       <c r="W172" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="16.5" hidden="1">
       <c r="A173" s="2" t="s">
         <v>760</v>
       </c>
@@ -18294,7 +18288,7 @@
       <c r="V173" s="9"/>
       <c r="W173" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="16.5" hidden="1">
       <c r="A174" s="2" t="s">
         <v>760</v>
       </c>
@@ -18353,7 +18347,7 @@
       <c r="V174" s="9"/>
       <c r="W174" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="16.5" hidden="1">
       <c r="A175" s="2" t="s">
         <v>760</v>
       </c>
@@ -18412,7 +18406,7 @@
       <c r="V175" s="9"/>
       <c r="W175" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="16.5" hidden="1">
       <c r="A176" s="2" t="s">
         <v>760</v>
       </c>
@@ -18475,7 +18469,7 @@
       <c r="V176" s="9"/>
       <c r="W176" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="25.5">
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="16.5" hidden="1">
       <c r="A177" s="2" t="s">
         <v>760</v>
       </c>
@@ -18538,7 +18532,7 @@
       <c r="V177" s="9"/>
       <c r="W177" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="16.5" hidden="1">
       <c r="A178" s="2" t="s">
         <v>760</v>
       </c>
@@ -18597,7 +18591,7 @@
       <c r="V178" s="9"/>
       <c r="W178" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="16.5" hidden="1">
       <c r="A179" s="2" t="s">
         <v>760</v>
       </c>
@@ -18656,7 +18650,7 @@
       <c r="V179" s="9"/>
       <c r="W179" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="16.5" hidden="1">
       <c r="A180" s="2" t="s">
         <v>760</v>
       </c>
@@ -18715,7 +18709,7 @@
       <c r="V180" s="9"/>
       <c r="W180" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="16.5" hidden="1">
       <c r="A181" s="2" t="s">
         <v>760</v>
       </c>
@@ -18774,7 +18768,7 @@
       <c r="V181" s="9"/>
       <c r="W181" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="16.5" hidden="1">
       <c r="A182" s="2" t="s">
         <v>830</v>
       </c>
@@ -18833,7 +18827,7 @@
       <c r="V182" s="9"/>
       <c r="W182" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="16.5" hidden="1">
       <c r="A183" s="2" t="s">
         <v>830</v>
       </c>
@@ -18892,7 +18886,7 @@
       <c r="V183" s="9"/>
       <c r="W183" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="16.5" hidden="1">
       <c r="A184" s="2" t="s">
         <v>830</v>
       </c>
@@ -18955,7 +18949,7 @@
       <c r="V184" s="9"/>
       <c r="W184" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="16.5" hidden="1">
       <c r="A185" s="2" t="s">
         <v>830</v>
       </c>
@@ -19014,7 +19008,7 @@
       <c r="V185" s="9"/>
       <c r="W185" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="16.5" hidden="1">
       <c r="A186" s="2" t="s">
         <v>830</v>
       </c>
@@ -19077,7 +19071,7 @@
       <c r="V186" s="9"/>
       <c r="W186" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="16.5" hidden="1">
       <c r="A187" s="2" t="s">
         <v>830</v>
       </c>
@@ -19136,7 +19130,7 @@
       <c r="V187" s="9"/>
       <c r="W187" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="16.5" hidden="1">
       <c r="A188" s="2" t="s">
         <v>830</v>
       </c>
@@ -19195,7 +19189,7 @@
       <c r="V188" s="9"/>
       <c r="W188" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="16.5" hidden="1">
       <c r="A189" s="2" t="s">
         <v>830</v>
       </c>
@@ -19254,7 +19248,7 @@
       <c r="V189" s="9"/>
       <c r="W189" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="16.5" hidden="1">
       <c r="A190" s="2" t="s">
         <v>830</v>
       </c>
@@ -19313,7 +19307,7 @@
       <c r="V190" s="9"/>
       <c r="W190" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="16.5" hidden="1">
       <c r="A191" s="2" t="s">
         <v>830</v>
       </c>
@@ -19372,7 +19366,7 @@
       <c r="V191" s="9"/>
       <c r="W191" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="16.5" hidden="1">
       <c r="A192" s="2" t="s">
         <v>830</v>
       </c>
@@ -19431,7 +19425,7 @@
       <c r="V192" s="9"/>
       <c r="W192" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="16.5" hidden="1">
       <c r="A193" s="2" t="s">
         <v>830</v>
       </c>
@@ -19490,7 +19484,7 @@
       <c r="V193" s="9"/>
       <c r="W193" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="16.5" hidden="1">
       <c r="A194" s="2" t="s">
         <v>830</v>
       </c>
@@ -19549,7 +19543,7 @@
       <c r="V194" s="9"/>
       <c r="W194" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="16.5" hidden="1">
       <c r="A195" s="2" t="s">
         <v>830</v>
       </c>
@@ -19608,7 +19602,7 @@
       <c r="V195" s="9"/>
       <c r="W195" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="16.5" hidden="1">
       <c r="A196" s="2" t="s">
         <v>830</v>
       </c>
@@ -19667,7 +19661,7 @@
       <c r="V196" s="9"/>
       <c r="W196" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="16.5" hidden="1">
       <c r="A197" s="2" t="s">
         <v>830</v>
       </c>
@@ -19730,7 +19724,7 @@
       <c r="V197" s="9"/>
       <c r="W197" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="16.5" hidden="1">
       <c r="A198" s="2" t="s">
         <v>830</v>
       </c>
@@ -19793,7 +19787,7 @@
       <c r="V198" s="9"/>
       <c r="W198" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="16.5" hidden="1">
       <c r="A199" s="2" t="s">
         <v>830</v>
       </c>
@@ -19852,7 +19846,7 @@
       <c r="V199" s="9"/>
       <c r="W199" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="16.5" hidden="1">
       <c r="A200" s="2" t="s">
         <v>830</v>
       </c>
@@ -19911,7 +19905,7 @@
       <c r="V200" s="9"/>
       <c r="W200" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="16.5" hidden="1">
       <c r="A201" s="2" t="s">
         <v>830</v>
       </c>
@@ -19970,7 +19964,7 @@
       <c r="V201" s="9"/>
       <c r="W201" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="16.5" hidden="1">
       <c r="A202" s="2" t="s">
         <v>830</v>
       </c>
@@ -20029,7 +20023,7 @@
       <c r="V202" s="9"/>
       <c r="W202" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="16.5" hidden="1">
       <c r="A203" s="2" t="s">
         <v>830</v>
       </c>
@@ -20092,7 +20086,7 @@
       <c r="V203" s="9"/>
       <c r="W203" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="16.5" hidden="1">
       <c r="A204" s="2" t="s">
         <v>830</v>
       </c>
@@ -20151,7 +20145,7 @@
       <c r="V204" s="9"/>
       <c r="W204" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="16.5" hidden="1">
       <c r="A205" s="2" t="s">
         <v>830</v>
       </c>
@@ -20210,7 +20204,7 @@
       <c r="V205" s="9"/>
       <c r="W205" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="16.5" hidden="1">
       <c r="A206" s="2" t="s">
         <v>830</v>
       </c>
@@ -20269,7 +20263,7 @@
       <c r="V206" s="9"/>
       <c r="W206" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="16.5" hidden="1">
       <c r="A207" s="2" t="s">
         <v>830</v>
       </c>
@@ -20328,7 +20322,7 @@
       <c r="V207" s="9"/>
       <c r="W207" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="16.5" hidden="1">
       <c r="A208" s="2" t="s">
         <v>830</v>
       </c>
@@ -20387,7 +20381,7 @@
       <c r="V208" s="9"/>
       <c r="W208" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="16.5" hidden="1">
       <c r="A209" s="2" t="s">
         <v>830</v>
       </c>
@@ -20446,7 +20440,7 @@
       <c r="V209" s="9"/>
       <c r="W209" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="16.5" hidden="1">
       <c r="A210" s="2" t="s">
         <v>830</v>
       </c>
@@ -20505,7 +20499,7 @@
       <c r="V210" s="9"/>
       <c r="W210" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="16.5" hidden="1">
       <c r="A211" s="2" t="s">
         <v>830</v>
       </c>
@@ -20564,7 +20558,7 @@
       <c r="V211" s="9"/>
       <c r="W211" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="16.5" hidden="1">
       <c r="A212" s="2" t="s">
         <v>830</v>
       </c>
@@ -20623,7 +20617,7 @@
       <c r="V212" s="9"/>
       <c r="W212" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="16.5" hidden="1">
       <c r="A213" s="2" t="s">
         <v>830</v>
       </c>
@@ -20682,7 +20676,7 @@
       <c r="V213" s="9"/>
       <c r="W213" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="16.5" hidden="1">
       <c r="A214" s="2" t="s">
         <v>956</v>
       </c>
@@ -20741,7 +20735,7 @@
       <c r="V214" s="9"/>
       <c r="W214" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="16.5" hidden="1">
       <c r="A215" s="2" t="s">
         <v>956</v>
       </c>
@@ -20800,7 +20794,7 @@
       <c r="V215" s="9"/>
       <c r="W215" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="16.5" hidden="1">
       <c r="A216" s="2" t="s">
         <v>956</v>
       </c>
@@ -20861,7 +20855,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="16.5" hidden="1">
       <c r="A217" s="2" t="s">
         <v>956</v>
       </c>
@@ -20922,7 +20916,7 @@
         <v>975</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="16.5" hidden="1">
       <c r="A218" s="2" t="s">
         <v>956</v>
       </c>
@@ -20983,7 +20977,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="16.5" hidden="1">
       <c r="A219" s="2" t="s">
         <v>956</v>
       </c>
@@ -21044,7 +21038,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="16.5" hidden="1">
       <c r="A220" s="2" t="s">
         <v>956</v>
       </c>
@@ -21103,7 +21097,7 @@
       <c r="V220" s="9"/>
       <c r="W220" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="16.5" hidden="1">
       <c r="A221" s="2" t="s">
         <v>956</v>
       </c>
@@ -21162,7 +21156,7 @@
       <c r="V221" s="9"/>
       <c r="W221" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="16.5" hidden="1">
       <c r="A222" s="2" t="s">
         <v>956</v>
       </c>
@@ -21221,7 +21215,7 @@
       <c r="V222" s="9"/>
       <c r="W222" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="16.5" hidden="1">
       <c r="A223" s="2" t="s">
         <v>956</v>
       </c>
@@ -21282,7 +21276,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="16.5" hidden="1">
       <c r="A224" s="2" t="s">
         <v>956</v>
       </c>
@@ -21341,7 +21335,7 @@
       <c r="V224" s="9"/>
       <c r="W224" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="16.5" hidden="1">
       <c r="A225" s="2" t="s">
         <v>956</v>
       </c>
@@ -21400,7 +21394,7 @@
       <c r="V225" s="9"/>
       <c r="W225" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="16.5" hidden="1">
       <c r="A226" s="2" t="s">
         <v>956</v>
       </c>
@@ -21459,7 +21453,7 @@
       <c r="V226" s="9"/>
       <c r="W226" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="16.5" hidden="1">
       <c r="A227" s="2" t="s">
         <v>956</v>
       </c>
@@ -21518,7 +21512,7 @@
       <c r="V227" s="9"/>
       <c r="W227" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="16.5" hidden="1">
       <c r="A228" s="2" t="s">
         <v>956</v>
       </c>
@@ -21581,7 +21575,7 @@
       <c r="V228" s="9"/>
       <c r="W228" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="16.5" hidden="1">
       <c r="A229" s="2" t="s">
         <v>956</v>
       </c>
@@ -21644,7 +21638,7 @@
       <c r="V229" s="9"/>
       <c r="W229" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="16.5" hidden="1">
       <c r="A230" s="2" t="s">
         <v>956</v>
       </c>
@@ -21703,7 +21697,7 @@
       <c r="V230" s="9"/>
       <c r="W230" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="16.5" hidden="1">
       <c r="A231" s="2" t="s">
         <v>956</v>
       </c>
@@ -21762,7 +21756,7 @@
       <c r="V231" s="9"/>
       <c r="W231" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="16.5" hidden="1">
       <c r="A232" s="2" t="s">
         <v>956</v>
       </c>
@@ -21821,7 +21815,7 @@
       <c r="V232" s="9"/>
       <c r="W232" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="16.5" hidden="1">
       <c r="A233" s="2" t="s">
         <v>956</v>
       </c>
@@ -21880,7 +21874,7 @@
       <c r="V233" s="9"/>
       <c r="W233" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="16.5" hidden="1">
       <c r="A234" s="2" t="s">
         <v>956</v>
       </c>
@@ -21939,7 +21933,7 @@
       <c r="V234" s="9"/>
       <c r="W234" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="16.5" hidden="1">
       <c r="A235" s="2" t="s">
         <v>956</v>
       </c>
@@ -21998,7 +21992,7 @@
       <c r="V235" s="9"/>
       <c r="W235" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="16.5" hidden="1">
       <c r="A236" s="2" t="s">
         <v>956</v>
       </c>
@@ -22057,7 +22051,7 @@
       <c r="V236" s="9"/>
       <c r="W236" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="16.5" hidden="1">
       <c r="A237" s="2" t="s">
         <v>956</v>
       </c>
@@ -22116,7 +22110,7 @@
       <c r="V237" s="9"/>
       <c r="W237" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="16.5" hidden="1">
       <c r="A238" s="2" t="s">
         <v>956</v>
       </c>
@@ -22177,7 +22171,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="16.5" hidden="1">
       <c r="A239" s="2" t="s">
         <v>956</v>
       </c>
@@ -22236,7 +22230,7 @@
       <c r="V239" s="9"/>
       <c r="W239" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="16.5" hidden="1">
       <c r="A240" s="2" t="s">
         <v>956</v>
       </c>
@@ -22295,7 +22289,7 @@
       <c r="V240" s="9"/>
       <c r="W240" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="16.5" hidden="1">
       <c r="A241" s="2" t="s">
         <v>956</v>
       </c>
@@ -22354,7 +22348,7 @@
       <c r="V241" s="9"/>
       <c r="W241" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="16.5" hidden="1">
       <c r="A242" s="2" t="s">
         <v>956</v>
       </c>
@@ -22413,7 +22407,7 @@
       <c r="V242" s="9"/>
       <c r="W242" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="16.5" hidden="1">
       <c r="A243" s="2" t="s">
         <v>956</v>
       </c>
@@ -22472,7 +22466,7 @@
       <c r="V243" s="9"/>
       <c r="W243" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="16.5" hidden="1">
       <c r="A244" s="2" t="s">
         <v>956</v>
       </c>
@@ -22531,7 +22525,7 @@
       <c r="V244" s="9"/>
       <c r="W244" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="16.5" hidden="1">
       <c r="A245" s="2" t="s">
         <v>956</v>
       </c>
@@ -22590,7 +22584,7 @@
       <c r="V245" s="9"/>
       <c r="W245" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="16.5" hidden="1">
       <c r="A246" s="2" t="s">
         <v>956</v>
       </c>
@@ -22649,7 +22643,7 @@
       <c r="V246" s="9"/>
       <c r="W246" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="16.5" hidden="1">
       <c r="A247" s="2" t="s">
         <v>956</v>
       </c>
@@ -22708,7 +22702,7 @@
       <c r="V247" s="9"/>
       <c r="W247" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="16.5" hidden="1">
       <c r="A248" s="2" t="s">
         <v>956</v>
       </c>
@@ -22767,7 +22761,7 @@
       <c r="V248" s="9"/>
       <c r="W248" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="16.5" hidden="1">
       <c r="A249" s="2" t="s">
         <v>1103</v>
       </c>
@@ -22826,7 +22820,7 @@
       <c r="V249" s="9"/>
       <c r="W249" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="16.5" hidden="1">
       <c r="A250" s="2" t="s">
         <v>1103</v>
       </c>
@@ -22885,7 +22879,7 @@
       <c r="V250" s="9"/>
       <c r="W250" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="16.5" hidden="1">
       <c r="A251" s="2" t="s">
         <v>1103</v>
       </c>
@@ -22944,7 +22938,7 @@
       <c r="V251" s="9"/>
       <c r="W251" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="16.5" hidden="1">
       <c r="A252" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23003,7 +22997,7 @@
       <c r="V252" s="9"/>
       <c r="W252" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="16.5" hidden="1">
       <c r="A253" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23066,7 +23060,7 @@
       <c r="V253" s="9"/>
       <c r="W253" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="16.5" hidden="1">
       <c r="A254" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23125,7 +23119,7 @@
       <c r="V254" s="9"/>
       <c r="W254" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="16.5" hidden="1">
       <c r="A255" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23188,7 +23182,7 @@
       <c r="V255" s="9"/>
       <c r="W255" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="16.5" hidden="1">
       <c r="A256" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23247,7 +23241,7 @@
       <c r="V256" s="9"/>
       <c r="W256" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="16.5" hidden="1">
       <c r="A257" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23306,7 +23300,7 @@
       <c r="V257" s="9"/>
       <c r="W257" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="16.5" hidden="1">
       <c r="A258" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23369,7 +23363,7 @@
       <c r="V258" s="9"/>
       <c r="W258" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="16.5" hidden="1">
       <c r="A259" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23428,7 +23422,7 @@
       <c r="V259" s="9"/>
       <c r="W259" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="16.5" hidden="1">
       <c r="A260" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23487,7 +23481,7 @@
       <c r="V260" s="9"/>
       <c r="W260" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="16.5" hidden="1">
       <c r="A261" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23546,7 +23540,7 @@
       <c r="V261" s="9"/>
       <c r="W261" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="16.5" hidden="1">
       <c r="A262" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23609,7 +23603,7 @@
       <c r="V262" s="9"/>
       <c r="W262" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="16.5" hidden="1">
       <c r="A263" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23668,7 +23662,7 @@
       <c r="V263" s="9"/>
       <c r="W263" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="16.5" hidden="1">
       <c r="A264" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23727,7 +23721,7 @@
       <c r="V264" s="9"/>
       <c r="W264" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="16.5" hidden="1">
       <c r="A265" s="2" t="s">
         <v>1103</v>
       </c>
@@ -23786,7 +23780,7 @@
       <c r="V265" s="9"/>
       <c r="W265" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="16.5" hidden="1">
       <c r="A266" s="2" t="s">
         <v>1172</v>
       </c>
@@ -23847,7 +23841,7 @@
       <c r="V266" s="9"/>
       <c r="W266" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="16.5" hidden="1">
       <c r="A267" s="2" t="s">
         <v>1172</v>
       </c>
@@ -23906,7 +23900,7 @@
       <c r="V267" s="9"/>
       <c r="W267" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="16.5" hidden="1">
       <c r="A268" s="2" t="s">
         <v>1172</v>
       </c>
@@ -23967,7 +23961,7 @@
       <c r="V268" s="9"/>
       <c r="W268" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="16.5" hidden="1">
       <c r="A269" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24028,7 +24022,7 @@
       <c r="V269" s="9"/>
       <c r="W269" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="16.5" hidden="1">
       <c r="A270" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24087,7 +24081,7 @@
       <c r="V270" s="9"/>
       <c r="W270" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="16.5" hidden="1">
       <c r="A271" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24146,7 +24140,7 @@
       <c r="V271" s="9"/>
       <c r="W271" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="16.5" hidden="1">
       <c r="A272" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24207,7 +24201,7 @@
       <c r="V272" s="9"/>
       <c r="W272" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="16.5" hidden="1">
       <c r="A273" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24268,7 +24262,7 @@
         <v>975</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="16.5" hidden="1">
       <c r="A274" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24329,7 +24323,7 @@
       <c r="V274" s="9"/>
       <c r="W274" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="16.5" hidden="1">
       <c r="A275" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24388,7 +24382,7 @@
       <c r="V275" s="9"/>
       <c r="W275" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="16.5" hidden="1">
       <c r="A276" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24451,7 +24445,7 @@
       <c r="V276" s="9"/>
       <c r="W276" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="16.5" hidden="1">
       <c r="A277" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24510,7 +24504,7 @@
       <c r="V277" s="9"/>
       <c r="W277" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="16.5" hidden="1">
       <c r="A278" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24569,7 +24563,7 @@
       <c r="V278" s="9"/>
       <c r="W278" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="16.5" hidden="1">
       <c r="A279" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24628,7 +24622,7 @@
       <c r="V279" s="9"/>
       <c r="W279" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="16.5" hidden="1">
       <c r="A280" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24687,7 +24681,7 @@
       <c r="V280" s="9"/>
       <c r="W280" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="16.5" hidden="1">
       <c r="A281" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24750,7 +24744,7 @@
       <c r="V281" s="9"/>
       <c r="W281" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="16.5" hidden="1">
       <c r="A282" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24809,7 +24803,7 @@
       <c r="V282" s="9"/>
       <c r="W282" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="16.5" hidden="1">
       <c r="A283" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24872,7 +24866,7 @@
       <c r="V283" s="9"/>
       <c r="W283" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="16.5" hidden="1">
       <c r="A284" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24931,7 +24925,7 @@
       <c r="V284" s="9"/>
       <c r="W284" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="16.5" hidden="1">
       <c r="A285" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24994,7 +24988,7 @@
       <c r="V285" s="9"/>
       <c r="W285" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="16.5" hidden="1">
       <c r="A286" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25053,7 +25047,7 @@
       <c r="V286" s="9"/>
       <c r="W286" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="16.5" hidden="1">
       <c r="A287" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25112,7 +25106,7 @@
       <c r="V287" s="9"/>
       <c r="W287" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="16.5" hidden="1">
       <c r="A288" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25171,7 +25165,7 @@
       <c r="V288" s="9"/>
       <c r="W288" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="16.5" hidden="1">
       <c r="A289" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25230,7 +25224,7 @@
       <c r="V289" s="9"/>
       <c r="W289" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="16.5" hidden="1">
       <c r="A290" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25293,7 +25287,7 @@
       <c r="V290" s="9"/>
       <c r="W290" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="16.5" hidden="1">
       <c r="A291" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25352,7 +25346,7 @@
       <c r="V291" s="9"/>
       <c r="W291" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="16.5" hidden="1">
       <c r="A292" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25411,7 +25405,7 @@
       <c r="V292" s="9"/>
       <c r="W292" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="16.5" hidden="1">
       <c r="A293" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25470,7 +25464,7 @@
       <c r="V293" s="9"/>
       <c r="W293" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="16.5" hidden="1">
       <c r="A294" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25533,7 +25527,7 @@
       <c r="V294" s="9"/>
       <c r="W294" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="16.5" hidden="1">
       <c r="A295" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25592,7 +25586,7 @@
       <c r="V295" s="9"/>
       <c r="W295" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="16.5" hidden="1">
       <c r="A296" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25651,7 +25645,7 @@
       <c r="V296" s="9"/>
       <c r="W296" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="16.5" hidden="1">
       <c r="A297" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25710,7 +25704,7 @@
       <c r="V297" s="9"/>
       <c r="W297" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="16.5" hidden="1">
       <c r="A298" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25773,7 +25767,7 @@
       <c r="V298" s="9"/>
       <c r="W298" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="16.5" hidden="1">
       <c r="A299" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25832,7 +25826,7 @@
       <c r="V299" s="9"/>
       <c r="W299" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="16.5" hidden="1">
       <c r="A300" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25891,7 +25885,7 @@
       <c r="V300" s="9"/>
       <c r="W300" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="16.5" hidden="1">
       <c r="A301" s="2" t="s">
         <v>1213</v>
       </c>
@@ -25954,7 +25948,7 @@
       <c r="V301" s="9"/>
       <c r="W301" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="16.5" hidden="1">
       <c r="A302" s="2" t="s">
         <v>1213</v>
       </c>
@@ -26013,7 +26007,7 @@
       <c r="V302" s="9"/>
       <c r="W302" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="16.5" hidden="1">
       <c r="A303" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26072,7 +26066,7 @@
       <c r="V303" s="9"/>
       <c r="W303" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="16.5" hidden="1">
       <c r="A304" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26131,7 +26125,7 @@
       <c r="V304" s="9"/>
       <c r="W304" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="16.5" hidden="1">
       <c r="A305" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26190,7 +26184,7 @@
       <c r="V305" s="9"/>
       <c r="W305" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="16.5" hidden="1">
       <c r="A306" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26249,7 +26243,7 @@
       <c r="V306" s="9"/>
       <c r="W306" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="16.5" hidden="1">
       <c r="A307" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26308,7 +26302,7 @@
       <c r="V307" s="9"/>
       <c r="W307" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="16.5" hidden="1">
       <c r="A308" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26367,7 +26361,7 @@
       <c r="V308" s="9"/>
       <c r="W308" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="16.5" hidden="1">
       <c r="A309" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26436,7 +26430,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="16.5" hidden="1">
       <c r="A310" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26499,7 +26493,7 @@
       <c r="V310" s="9"/>
       <c r="W310" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="16.5" hidden="1">
       <c r="A311" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26558,7 +26552,7 @@
       <c r="V311" s="9"/>
       <c r="W311" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="16.5" hidden="1">
       <c r="A312" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26621,7 +26615,7 @@
       <c r="V312" s="9"/>
       <c r="W312" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="16.5" hidden="1">
       <c r="A313" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26680,7 +26674,7 @@
       <c r="V313" s="9"/>
       <c r="W313" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="16.5" hidden="1">
       <c r="A314" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26739,7 +26733,7 @@
       <c r="V314" s="9"/>
       <c r="W314" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="16.5" hidden="1">
       <c r="A315" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26798,7 +26792,7 @@
       <c r="V315" s="9"/>
       <c r="W315" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="16.5" hidden="1">
       <c r="A316" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26861,7 +26855,7 @@
       <c r="V316" s="9"/>
       <c r="W316" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="16.5" hidden="1">
       <c r="A317" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26920,7 +26914,7 @@
       <c r="V317" s="9"/>
       <c r="W317" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="16.5" hidden="1">
       <c r="A318" s="2" t="s">
         <v>1326</v>
       </c>
@@ -26979,7 +26973,7 @@
       <c r="V318" s="9"/>
       <c r="W318" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="16.5" hidden="1">
       <c r="A319" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27038,7 +27032,7 @@
       <c r="V319" s="9"/>
       <c r="W319" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="16.5" hidden="1">
       <c r="A320" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27097,7 +27091,7 @@
       <c r="V320" s="9"/>
       <c r="W320" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="16.5" hidden="1">
       <c r="A321" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27156,7 +27150,7 @@
       <c r="V321" s="9"/>
       <c r="W321" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="16.5" hidden="1">
       <c r="A322" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27219,7 +27213,7 @@
       <c r="V322" s="9"/>
       <c r="W322" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="16.5" hidden="1">
       <c r="A323" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27278,7 +27272,7 @@
       <c r="V323" s="9"/>
       <c r="W323" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="16.5" hidden="1">
       <c r="A324" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27337,7 +27331,7 @@
       <c r="V324" s="9"/>
       <c r="W324" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="16.5" hidden="1">
       <c r="A325" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27408,7 +27402,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="16.5" hidden="1">
       <c r="A326" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27471,7 +27465,7 @@
       <c r="V326" s="9"/>
       <c r="W326" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="16.5" hidden="1">
       <c r="A327" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27530,7 +27524,7 @@
       <c r="V327" s="9"/>
       <c r="W327" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="16.5" hidden="1">
       <c r="A328" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27589,7 +27583,7 @@
       <c r="V328" s="9"/>
       <c r="W328" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="16.5" hidden="1">
       <c r="A329" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27648,7 +27642,7 @@
       <c r="V329" s="9"/>
       <c r="W329" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="16.5" hidden="1">
       <c r="A330" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27707,7 +27701,7 @@
       <c r="V330" s="9"/>
       <c r="W330" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="16.5" hidden="1">
       <c r="A331" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27766,7 +27760,7 @@
       <c r="V331" s="9"/>
       <c r="W331" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="16.5" hidden="1">
       <c r="A332" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27829,7 +27823,7 @@
       <c r="V332" s="9"/>
       <c r="W332" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="16.5" hidden="1">
       <c r="A333" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27888,7 +27882,7 @@
       <c r="V333" s="9"/>
       <c r="W333" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="16.5" hidden="1">
       <c r="A334" s="2" t="s">
         <v>1326</v>
       </c>
@@ -27947,7 +27941,7 @@
       <c r="V334" s="9"/>
       <c r="W334" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="16.5" hidden="1">
       <c r="A335" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28006,7 +28000,7 @@
       <c r="V335" s="9"/>
       <c r="W335" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="16.5" hidden="1">
       <c r="A336" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28065,7 +28059,7 @@
       <c r="V336" s="9"/>
       <c r="W336" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="16.5" hidden="1">
       <c r="A337" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28124,7 +28118,7 @@
       <c r="V337" s="9"/>
       <c r="W337" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="16.5" hidden="1">
       <c r="A338" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28183,7 +28177,7 @@
       <c r="V338" s="9"/>
       <c r="W338" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="16.5" hidden="1">
       <c r="A339" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28246,7 +28240,7 @@
       <c r="V339" s="9"/>
       <c r="W339" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="16.5" hidden="1">
       <c r="A340" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28305,7 +28299,7 @@
       <c r="V340" s="9"/>
       <c r="W340" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="16.5" hidden="1">
       <c r="A341" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28368,7 +28362,7 @@
       <c r="V341" s="9"/>
       <c r="W341" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="16.5" hidden="1">
       <c r="A342" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28427,7 +28421,7 @@
       <c r="V342" s="9"/>
       <c r="W342" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="16.5" hidden="1">
       <c r="A343" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28490,7 +28484,7 @@
       <c r="V343" s="9"/>
       <c r="W343" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="16.5" hidden="1">
       <c r="A344" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28549,7 +28543,7 @@
       <c r="V344" s="9"/>
       <c r="W344" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="16.5" hidden="1">
       <c r="A345" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28608,7 +28602,7 @@
       <c r="V345" s="9"/>
       <c r="W345" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="16.5" hidden="1">
       <c r="A346" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28667,7 +28661,7 @@
       <c r="V346" s="9"/>
       <c r="W346" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="16.5" hidden="1">
       <c r="A347" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28726,7 +28720,7 @@
       <c r="V347" s="9"/>
       <c r="W347" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="16.5" hidden="1">
       <c r="A348" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28785,7 +28779,7 @@
       <c r="V348" s="9"/>
       <c r="W348" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="16.5" hidden="1">
       <c r="A349" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28844,7 +28838,7 @@
       <c r="V349" s="9"/>
       <c r="W349" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="16.5" hidden="1">
       <c r="A350" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28903,7 +28897,7 @@
       <c r="V350" s="9"/>
       <c r="W350" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="16.5" hidden="1">
       <c r="A351" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28962,7 +28956,7 @@
       <c r="V351" s="9"/>
       <c r="W351" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="16.5" hidden="1">
       <c r="A352" s="2" t="s">
         <v>1326</v>
       </c>
@@ -29021,7 +29015,7 @@
       <c r="V352" s="9"/>
       <c r="W352" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="16.5" hidden="1">
       <c r="A353" s="2" t="s">
         <v>1326</v>
       </c>
@@ -29080,7 +29074,7 @@
       <c r="V353" s="9"/>
       <c r="W353" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="16.5" hidden="1">
       <c r="A354" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29141,7 +29135,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="16.5" hidden="1">
       <c r="A355" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29200,7 +29194,7 @@
       <c r="V355" s="9"/>
       <c r="W355" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="16.5" hidden="1">
       <c r="A356" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29261,7 +29255,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="16.5" hidden="1">
       <c r="A357" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29322,7 +29316,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="16.5" hidden="1">
       <c r="A358" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29383,7 +29377,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="16.5" hidden="1">
       <c r="A359" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29442,7 +29436,7 @@
       <c r="V359" s="9"/>
       <c r="W359" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="16.5" hidden="1">
       <c r="A360" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29501,7 +29495,7 @@
       <c r="V360" s="9"/>
       <c r="W360" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="16.5" hidden="1">
       <c r="A361" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29560,7 +29554,7 @@
       <c r="V361" s="9"/>
       <c r="W361" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="16.5" hidden="1">
       <c r="A362" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29619,7 +29613,7 @@
       <c r="V362" s="9"/>
       <c r="W362" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="16.5" hidden="1">
       <c r="A363" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29678,7 +29672,7 @@
       <c r="V363" s="9"/>
       <c r="W363" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="16.5" hidden="1">
       <c r="A364" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29737,7 +29731,7 @@
       <c r="V364" s="9"/>
       <c r="W364" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="16.5" hidden="1">
       <c r="A365" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29796,7 +29790,7 @@
       <c r="V365" s="9"/>
       <c r="W365" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="16.5" hidden="1">
       <c r="A366" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29855,7 +29849,7 @@
       <c r="V366" s="9"/>
       <c r="W366" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="16.5" hidden="1">
       <c r="A367" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29914,7 +29908,7 @@
       <c r="V367" s="9"/>
       <c r="W367" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="16.5" hidden="1">
       <c r="A368" s="2" t="s">
         <v>1538</v>
       </c>
@@ -29973,7 +29967,7 @@
       <c r="V368" s="9"/>
       <c r="W368" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="16.5" hidden="1">
       <c r="A369" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30032,7 +30026,7 @@
       <c r="V369" s="9"/>
       <c r="W369" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="16.5" hidden="1">
       <c r="A370" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30091,7 +30085,7 @@
       <c r="V370" s="9"/>
       <c r="W370" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="16.5" hidden="1">
       <c r="A371" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30150,7 +30144,7 @@
       <c r="V371" s="9"/>
       <c r="W371" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="16.5" hidden="1">
       <c r="A372" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30209,7 +30203,7 @@
       <c r="V372" s="9"/>
       <c r="W372" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="16.5" hidden="1">
       <c r="A373" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30270,7 +30264,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="16.5" hidden="1">
       <c r="A374" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30329,7 +30323,7 @@
       <c r="V374" s="9"/>
       <c r="W374" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="16.5" hidden="1">
       <c r="A375" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30388,7 +30382,7 @@
       <c r="V375" s="9"/>
       <c r="W375" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="16.5" hidden="1">
       <c r="A376" s="2" t="s">
         <v>1538</v>
       </c>
@@ -30447,7 +30441,7 @@
       <c r="V376" s="9"/>
       <c r="W376" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="16.5" hidden="1">
       <c r="A377" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30508,7 +30502,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="16.5" hidden="1">
       <c r="A378" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30569,7 +30563,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="16.5" hidden="1">
       <c r="A379" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30628,7 +30622,7 @@
       <c r="V379" s="9"/>
       <c r="W379" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="16.5" hidden="1">
       <c r="A380" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30687,7 +30681,7 @@
       <c r="V380" s="9"/>
       <c r="W380" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="16.5" hidden="1">
       <c r="A381" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30750,7 +30744,7 @@
       <c r="V381" s="9"/>
       <c r="W381" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="16.5" hidden="1">
       <c r="A382" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30811,7 +30805,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="16.5" hidden="1">
       <c r="A383" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30870,7 +30864,7 @@
       <c r="V383" s="9"/>
       <c r="W383" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="16.5" hidden="1">
       <c r="A384" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30929,7 +30923,7 @@
       <c r="V384" s="9"/>
       <c r="W384" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="16.5" hidden="1">
       <c r="A385" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30990,7 +30984,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="16.5" hidden="1">
       <c r="A386" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31051,7 +31045,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="16.5" hidden="1">
       <c r="A387" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31110,7 +31104,7 @@
       <c r="V387" s="9"/>
       <c r="W387" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="16.5" hidden="1">
       <c r="A388" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31173,7 +31167,7 @@
       <c r="V388" s="9"/>
       <c r="W388" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="16.5" hidden="1">
       <c r="A389" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31232,7 +31226,7 @@
       <c r="V389" s="9"/>
       <c r="W389" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="16.5" hidden="1">
       <c r="A390" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31291,7 +31285,7 @@
       <c r="V390" s="9"/>
       <c r="W390" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="16.5" hidden="1">
       <c r="A391" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31350,7 +31344,7 @@
       <c r="V391" s="9"/>
       <c r="W391" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="16.5" hidden="1">
       <c r="A392" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31409,7 +31403,7 @@
       <c r="V392" s="9"/>
       <c r="W392" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="16.5" hidden="1">
       <c r="A393" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31468,7 +31462,7 @@
       <c r="V393" s="9"/>
       <c r="W393" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="16.5" hidden="1">
       <c r="A394" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31527,7 +31521,7 @@
       <c r="V394" s="9"/>
       <c r="W394" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="16.5" hidden="1">
       <c r="A395" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31586,7 +31580,7 @@
       <c r="V395" s="9"/>
       <c r="W395" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="16.5" hidden="1">
       <c r="A396" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31645,7 +31639,7 @@
       <c r="V396" s="9"/>
       <c r="W396" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="16.5" hidden="1">
       <c r="A397" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31704,7 +31698,7 @@
       <c r="V397" s="9"/>
       <c r="W397" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="16.5" hidden="1">
       <c r="A398" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31765,7 +31759,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="16.5" hidden="1">
       <c r="A399" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31826,7 +31820,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="16.5" hidden="1">
       <c r="A400" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31885,7 +31879,7 @@
       <c r="V400" s="9"/>
       <c r="W400" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="16.5" hidden="1">
       <c r="A401" s="2" t="s">
         <v>1630</v>
       </c>
@@ -31946,7 +31940,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="16.5" hidden="1">
       <c r="A402" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32007,7 +32001,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="16.5" hidden="1">
       <c r="A403" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32068,7 +32062,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="16.5" hidden="1">
       <c r="A404" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32127,7 +32121,7 @@
       <c r="V404" s="9"/>
       <c r="W404" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="16.5" hidden="1">
       <c r="A405" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32186,7 +32180,7 @@
       <c r="V405" s="9"/>
       <c r="W405" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="16.5" hidden="1">
       <c r="A406" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32247,7 +32241,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="16.5" hidden="1">
       <c r="A407" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32306,7 +32300,7 @@
       <c r="V407" s="9"/>
       <c r="W407" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="16.5" hidden="1">
       <c r="A408" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32365,7 +32359,7 @@
       <c r="V408" s="9"/>
       <c r="W408" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="16.5" hidden="1">
       <c r="A409" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32424,7 +32418,7 @@
       <c r="V409" s="9"/>
       <c r="W409" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="16.5" hidden="1">
       <c r="A410" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32483,7 +32477,7 @@
       <c r="V410" s="9"/>
       <c r="W410" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="16.5" hidden="1">
       <c r="A411" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32542,7 +32536,7 @@
       <c r="V411" s="9"/>
       <c r="W411" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="16.5" hidden="1">
       <c r="A412" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32605,7 +32599,7 @@
       <c r="V412" s="9"/>
       <c r="W412" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="16.5" hidden="1">
       <c r="A413" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32666,7 +32660,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="16.5" hidden="1">
       <c r="A414" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32727,7 +32721,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="16.5" hidden="1">
       <c r="A415" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32786,7 +32780,7 @@
       <c r="V415" s="9"/>
       <c r="W415" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="16.5" hidden="1">
       <c r="A416" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32845,7 +32839,7 @@
       <c r="V416" s="9"/>
       <c r="W416" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="16.5" hidden="1">
       <c r="A417" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32904,7 +32898,7 @@
       <c r="V417" s="9"/>
       <c r="W417" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="16.5" hidden="1">
       <c r="A418" s="2" t="s">
         <v>1630</v>
       </c>
@@ -32965,7 +32959,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="16.5" hidden="1">
       <c r="A419" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33026,7 +33020,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="16.5" hidden="1">
       <c r="A420" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33087,7 +33081,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="16.5" hidden="1">
       <c r="A421" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33148,7 +33142,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="16.5" hidden="1">
       <c r="A422" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33207,7 +33201,7 @@
       <c r="V422" s="9"/>
       <c r="W422" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="16.5" hidden="1">
       <c r="A423" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33268,7 +33262,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="16.5" hidden="1">
       <c r="A424" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33329,7 +33323,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="16.5" hidden="1">
       <c r="A425" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33392,7 +33386,7 @@
       <c r="V425" s="9"/>
       <c r="W425" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="16.5" hidden="1">
       <c r="A426" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33451,7 +33445,7 @@
       <c r="V426" s="9"/>
       <c r="W426" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="16.5" hidden="1">
       <c r="A427" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33512,7 +33506,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="16.5" hidden="1">
       <c r="A428" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33571,7 +33565,7 @@
       <c r="V428" s="9"/>
       <c r="W428" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="16.5" hidden="1">
       <c r="A429" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33632,7 +33626,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="16.5" hidden="1">
       <c r="A430" s="2" t="s">
         <v>1630</v>
       </c>
@@ -33693,7 +33687,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="16.5" hidden="1">
       <c r="A431" s="2" t="s">
         <v>1854</v>
       </c>
@@ -33752,7 +33746,7 @@
       <c r="V431" s="9"/>
       <c r="W431" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="16.5" hidden="1">
       <c r="A432" s="2" t="s">
         <v>1854</v>
       </c>
@@ -33811,7 +33805,7 @@
       <c r="V432" s="9"/>
       <c r="W432" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="16.5" hidden="1">
       <c r="A433" s="2" t="s">
         <v>1854</v>
       </c>
@@ -33870,7 +33864,7 @@
       <c r="V433" s="9"/>
       <c r="W433" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="16.5" hidden="1">
       <c r="A434" s="2" t="s">
         <v>1854</v>
       </c>
@@ -33933,7 +33927,7 @@
       <c r="V434" s="9"/>
       <c r="W434" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="16.5" hidden="1">
       <c r="A435" s="2" t="s">
         <v>1854</v>
       </c>
@@ -33992,7 +33986,7 @@
       <c r="V435" s="9"/>
       <c r="W435" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="16.5" hidden="1">
       <c r="A436" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34055,7 +34049,7 @@
       <c r="V436" s="9"/>
       <c r="W436" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="16.5" hidden="1">
       <c r="A437" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34114,7 +34108,7 @@
       <c r="V437" s="9"/>
       <c r="W437" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="16.5" hidden="1">
       <c r="A438" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34173,7 +34167,7 @@
       <c r="V438" s="9"/>
       <c r="W438" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="16.5" hidden="1">
       <c r="A439" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34232,7 +34226,7 @@
       <c r="V439" s="9"/>
       <c r="W439" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="16.5" hidden="1">
       <c r="A440" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34291,7 +34285,7 @@
       <c r="V440" s="9"/>
       <c r="W440" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="16.5" hidden="1">
       <c r="A441" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34350,7 +34344,7 @@
       <c r="V441" s="9"/>
       <c r="W441" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="16.5" hidden="1">
       <c r="A442" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34409,7 +34403,7 @@
       <c r="V442" s="9"/>
       <c r="W442" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="16.5" hidden="1">
       <c r="A443" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34468,7 +34462,7 @@
       <c r="V443" s="9"/>
       <c r="W443" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="16.5" hidden="1">
       <c r="A444" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34527,7 +34521,7 @@
       <c r="V444" s="9"/>
       <c r="W444" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="16.5" hidden="1">
       <c r="A445" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34586,7 +34580,7 @@
       <c r="V445" s="9"/>
       <c r="W445" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="16.5" hidden="1">
       <c r="A446" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34645,7 +34639,7 @@
       <c r="V446" s="9"/>
       <c r="W446" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="16.5" hidden="1">
       <c r="A447" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34704,7 +34698,7 @@
       <c r="V447" s="9"/>
       <c r="W447" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="16.5" hidden="1">
       <c r="A448" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34763,7 +34757,7 @@
       <c r="V448" s="9"/>
       <c r="W448" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="16.5" hidden="1">
       <c r="A449" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34826,7 +34820,7 @@
       <c r="V449" s="9"/>
       <c r="W449" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="16.5" hidden="1">
       <c r="A450" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34885,7 +34879,7 @@
       <c r="V450" s="9"/>
       <c r="W450" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="16.5" hidden="1">
       <c r="A451" s="2" t="s">
         <v>1854</v>
       </c>
@@ -34944,7 +34938,7 @@
       <c r="V451" s="9"/>
       <c r="W451" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="16.5" hidden="1">
       <c r="A452" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35003,7 +34997,7 @@
       <c r="V452" s="9"/>
       <c r="W452" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="16.5" hidden="1">
       <c r="A453" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35062,7 +35056,7 @@
       <c r="V453" s="9"/>
       <c r="W453" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="16.5" hidden="1">
       <c r="A454" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35125,7 +35119,7 @@
       <c r="V454" s="9"/>
       <c r="W454" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="16.5" hidden="1">
       <c r="A455" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35184,7 +35178,7 @@
       <c r="V455" s="9"/>
       <c r="W455" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="16.5" hidden="1">
       <c r="A456" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35247,7 +35241,7 @@
       <c r="V456" s="9"/>
       <c r="W456" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="16.5" hidden="1">
       <c r="A457" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35306,7 +35300,7 @@
       <c r="V457" s="9"/>
       <c r="W457" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="16.5" hidden="1">
       <c r="A458" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35365,7 +35359,7 @@
       <c r="V458" s="9"/>
       <c r="W458" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="16.5" hidden="1">
       <c r="A459" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35424,7 +35418,7 @@
       <c r="V459" s="9"/>
       <c r="W459" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="16.5" hidden="1">
       <c r="A460" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35483,7 +35477,7 @@
       <c r="V460" s="9"/>
       <c r="W460" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="16.5" hidden="1">
       <c r="A461" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35546,7 +35540,7 @@
       <c r="V461" s="9"/>
       <c r="W461" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="16.5" hidden="1">
       <c r="A462" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35605,7 +35599,7 @@
       <c r="V462" s="9"/>
       <c r="W462" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="16.5" hidden="1">
       <c r="A463" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35664,7 +35658,7 @@
       <c r="V463" s="9"/>
       <c r="W463" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="16.5" hidden="1">
       <c r="A464" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35723,7 +35717,7 @@
       <c r="V464" s="9"/>
       <c r="W464" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="16.5" hidden="1">
       <c r="A465" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35784,7 +35778,7 @@
       <c r="V465" s="9"/>
       <c r="W465" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="16.5" hidden="1">
       <c r="A466" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35843,7 +35837,7 @@
       <c r="V466" s="9"/>
       <c r="W466" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="16.5" hidden="1">
       <c r="A467" s="2" t="s">
         <v>1854</v>
       </c>
@@ -35902,7 +35896,7 @@
       <c r="V467" s="9"/>
       <c r="W467" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="16.5" hidden="1">
       <c r="A468" s="2" t="s">
         <v>2001</v>
       </c>
@@ -35961,7 +35955,7 @@
       <c r="V468" s="9"/>
       <c r="W468" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="16.5" hidden="1">
       <c r="A469" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36020,7 +36014,7 @@
       <c r="V469" s="9"/>
       <c r="W469" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="16.5" hidden="1">
       <c r="A470" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36079,7 +36073,7 @@
       <c r="V470" s="9"/>
       <c r="W470" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="16.5" hidden="1">
       <c r="A471" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36140,7 +36134,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="16.5" hidden="1">
       <c r="A472" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36199,7 +36193,7 @@
       <c r="V472" s="9"/>
       <c r="W472" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="16.5" hidden="1">
       <c r="A473" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36258,7 +36252,7 @@
       <c r="V473" s="9"/>
       <c r="W473" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="16.5" hidden="1">
       <c r="A474" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36317,7 +36311,7 @@
       <c r="V474" s="9"/>
       <c r="W474" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="16.5" hidden="1">
       <c r="A475" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36376,7 +36370,7 @@
       <c r="V475" s="9"/>
       <c r="W475" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="16.5" hidden="1">
       <c r="A476" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36435,7 +36429,7 @@
       <c r="V476" s="9"/>
       <c r="W476" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="16.5" hidden="1">
       <c r="A477" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36494,7 +36488,7 @@
       <c r="V477" s="9"/>
       <c r="W477" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="16.5" hidden="1">
       <c r="A478" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36557,7 +36551,7 @@
       <c r="V478" s="9"/>
       <c r="W478" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="16.5" hidden="1">
       <c r="A479" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36616,7 +36610,7 @@
       <c r="V479" s="9"/>
       <c r="W479" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="16.5" hidden="1">
       <c r="A480" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36675,7 +36669,7 @@
       <c r="V480" s="9"/>
       <c r="W480" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="16.5" hidden="1">
       <c r="A481" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36738,7 +36732,7 @@
       <c r="V481" s="9"/>
       <c r="W481" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="16.5" hidden="1">
       <c r="A482" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36797,7 +36791,7 @@
       <c r="V482" s="9"/>
       <c r="W482" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="16.5" hidden="1">
       <c r="A483" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36856,7 +36850,7 @@
       <c r="V483" s="9"/>
       <c r="W483" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="16.5" hidden="1">
       <c r="A484" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36915,7 +36909,7 @@
       <c r="V484" s="9"/>
       <c r="W484" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="16.5" hidden="1">
       <c r="A485" s="2" t="s">
         <v>2001</v>
       </c>
@@ -36974,7 +36968,7 @@
       <c r="V485" s="9"/>
       <c r="W485" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="16.5" hidden="1">
       <c r="A486" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37035,7 +37029,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="16.5" hidden="1">
       <c r="A487" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37096,7 +37090,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="16.5" hidden="1">
       <c r="A488" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37157,7 +37151,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="16.5" hidden="1">
       <c r="A489" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37216,7 +37210,7 @@
       <c r="V489" s="9"/>
       <c r="W489" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="16.5" hidden="1">
       <c r="A490" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37277,7 +37271,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="16.5" hidden="1">
       <c r="A491" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37338,7 +37332,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="16.5" hidden="1">
       <c r="A492" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37397,7 +37391,7 @@
       <c r="V492" s="9"/>
       <c r="W492" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="16.5" hidden="1">
       <c r="A493" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37458,7 +37452,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="16.5" hidden="1">
       <c r="A494" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37517,7 +37511,7 @@
       <c r="V494" s="9"/>
       <c r="W494" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="16.5" hidden="1">
       <c r="A495" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37578,7 +37572,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="16.5" hidden="1">
       <c r="A496" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37639,7 +37633,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="16.5" hidden="1">
       <c r="A497" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37700,7 +37694,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="16.5" hidden="1">
       <c r="A498" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37765,7 +37759,7 @@
       </c>
       <c r="W498" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="16.5" hidden="1">
       <c r="A499" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37826,7 +37820,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="16.5" hidden="1">
       <c r="A500" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37887,7 +37881,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="16.5" hidden="1">
       <c r="A501" s="2" t="s">
         <v>2072</v>
       </c>
@@ -37946,7 +37940,7 @@
       <c r="V501" s="9"/>
       <c r="W501" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="16.5" hidden="1">
       <c r="A502" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38005,7 +37999,7 @@
       <c r="V502" s="9"/>
       <c r="W502" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="16.5" hidden="1">
       <c r="A503" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38064,7 +38058,7 @@
       <c r="V503" s="9"/>
       <c r="W503" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="16.5" hidden="1">
       <c r="A504" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38125,7 +38119,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="16.5" hidden="1">
       <c r="A505" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38186,7 +38180,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="16.5" hidden="1">
       <c r="A506" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38245,7 +38239,7 @@
       <c r="V506" s="9"/>
       <c r="W506" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="16.5" hidden="1">
       <c r="A507" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38304,7 +38298,7 @@
       <c r="V507" s="9"/>
       <c r="W507" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="16.5" hidden="1">
       <c r="A508" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38363,7 +38357,7 @@
       <c r="V508" s="9"/>
       <c r="W508" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="16.5" hidden="1">
       <c r="A509" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38424,7 +38418,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="16.5" hidden="1">
       <c r="A510" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38485,7 +38479,7 @@
         <v>975</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="16.5" hidden="1">
       <c r="A511" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38544,7 +38538,7 @@
       <c r="V511" s="9"/>
       <c r="W511" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="16.5" hidden="1">
       <c r="A512" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38603,7 +38597,7 @@
       <c r="V512" s="9"/>
       <c r="W512" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="16.5" hidden="1">
       <c r="A513" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38664,7 +38658,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="16.5" hidden="1">
       <c r="A514" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38725,7 +38719,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="16.5" hidden="1">
       <c r="A515" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38786,7 +38780,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="16.5" hidden="1">
       <c r="A516" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38847,7 +38841,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="16.5" hidden="1">
       <c r="A517" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38906,7 +38900,7 @@
       <c r="V517" s="9"/>
       <c r="W517" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="16.5" hidden="1">
       <c r="A518" s="2" t="s">
         <v>2072</v>
       </c>
@@ -38967,7 +38961,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="16.5" hidden="1">
       <c r="A519" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39028,7 +39022,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="16.5" hidden="1">
       <c r="A520" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39089,7 +39083,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="16.5" hidden="1">
       <c r="A521" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39150,7 +39144,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="16.5" hidden="1">
       <c r="A522" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39211,7 +39205,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="16.5" hidden="1">
       <c r="A523" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39272,7 +39266,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="16.5" hidden="1">
       <c r="A524" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39333,7 +39327,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="16.5" hidden="1">
       <c r="A525" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39400,7 +39394,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="16.5" hidden="1">
       <c r="A526" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39459,7 +39453,7 @@
       <c r="V526" s="9"/>
       <c r="W526" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="16.5" hidden="1">
       <c r="A527" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39520,7 +39514,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="16.5" hidden="1">
       <c r="A528" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39579,7 +39573,7 @@
       <c r="V528" s="9"/>
       <c r="W528" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="16.5" hidden="1">
       <c r="A529" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39638,7 +39632,7 @@
       <c r="V529" s="9"/>
       <c r="W529" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="16.5" hidden="1">
       <c r="A530" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39697,7 +39691,7 @@
       <c r="V530" s="9"/>
       <c r="W530" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="16.5" hidden="1">
       <c r="A531" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39758,7 +39752,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="16.5" hidden="1">
       <c r="A532" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39819,7 +39813,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="16.5" hidden="1">
       <c r="A533" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39878,7 +39872,7 @@
       <c r="V533" s="9"/>
       <c r="W533" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="16.5" hidden="1">
       <c r="A534" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39939,7 +39933,7 @@
         <v>971</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="16.5" hidden="1">
       <c r="A535" s="2" t="s">
         <v>2072</v>
       </c>
@@ -39998,7 +39992,7 @@
       <c r="V535" s="9"/>
       <c r="W535" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="16.5" hidden="1">
       <c r="A536" s="2" t="s">
         <v>2072</v>
       </c>
@@ -40057,7 +40051,7 @@
       <c r="V536" s="9"/>
       <c r="W536" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="16.5" hidden="1">
       <c r="A537" s="2" t="s">
         <v>2072</v>
       </c>
